--- a/Jan 2026 COPY PUSHAdolescentDailyDiary_DATA_LABELS_7.2.2024_CLEANING_JA_KALIKA_11.24.2025_updated.xlsx
+++ b/Jan 2026 COPY PUSHAdolescentDailyDiary_DATA_LABELS_7.2.2024_CLEANING_JA_KALIKA_11.24.2025_updated.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\PUSH\Database\Daily Diaries\Daily Diary Cleaning October 2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ramsay/Desktop/STAT370E/STAT_370E_Repository/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="246" documentId="8_{ED39EE85-2D3F-469E-A94E-4A5E4B904BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6815983B-5832-463C-BE61-3B871149A6EB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61D6841-2BCB-8049-A814-0439C32C0449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45" yWindow="0" windowWidth="14700" windowHeight="15600" xr2:uid="{E3DD6756-11C2-49F3-9475-33832FAD117C}"/>
+    <workbookView xWindow="40" yWindow="660" windowWidth="14700" windowHeight="15600" xr2:uid="{E3DD6756-11C2-49F3-9475-33832FAD117C}"/>
   </bookViews>
   <sheets>
     <sheet name="PUSHAdolescentDailyDiary_DATA_L" sheetId="1" r:id="rId1"/>
@@ -644,7 +644,7 @@
     <numFmt numFmtId="164" formatCode="m/d;@"/>
     <numFmt numFmtId="165" formatCode="h:mm;@"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1127,7 +1127,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1140,7 +1140,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1517,36 +1516,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1E6EB76-6FFC-47D6-BB9C-97AA61C27599}">
   <dimension ref="A1:EU388"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" customWidth="1"/>
-    <col min="6" max="6" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="19.5" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" customWidth="1"/>
+    <col min="5" max="5" width="16.5" customWidth="1"/>
+    <col min="6" max="6" width="17.1640625" customWidth="1"/>
     <col min="7" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" customWidth="1"/>
-    <col min="12" max="12" width="17.42578125" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" customWidth="1"/>
-    <col min="17" max="17" width="15.85546875" customWidth="1"/>
+    <col min="11" max="11" width="14.5" customWidth="1"/>
+    <col min="12" max="12" width="17.5" customWidth="1"/>
+    <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5" customWidth="1"/>
+    <col min="17" max="17" width="15.83203125" customWidth="1"/>
     <col min="19" max="19" width="13" customWidth="1"/>
     <col min="20" max="20" width="14" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" customWidth="1"/>
-    <col min="23" max="23" width="13.85546875" customWidth="1"/>
-    <col min="24" max="24" width="13.28515625" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" customWidth="1"/>
-    <col min="26" max="26" width="13.28515625" customWidth="1"/>
+    <col min="21" max="21" width="14.6640625" customWidth="1"/>
+    <col min="22" max="22" width="14.5" customWidth="1"/>
+    <col min="23" max="23" width="13.83203125" customWidth="1"/>
+    <col min="24" max="24" width="13.33203125" customWidth="1"/>
+    <col min="25" max="25" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.33203125" customWidth="1"/>
     <col min="27" max="27" width="13" customWidth="1"/>
-    <col min="28" max="28" width="12.42578125" customWidth="1"/>
-    <col min="39" max="39" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.5" customWidth="1"/>
+    <col min="39" max="39" width="12.5" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:151" ht="22.5" customHeight="1">
+    <row r="1" spans="1:151" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="2" spans="1:151">
+    <row r="2" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>128</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:151">
+    <row r="3" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>128</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:151">
+    <row r="4" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>128</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:151">
+    <row r="5" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>128</v>
       </c>
@@ -3790,7 +3790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:151">
+    <row r="6" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>128</v>
       </c>
@@ -4237,7 +4237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:151">
+    <row r="7" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>128</v>
       </c>
@@ -4685,7 +4685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:151">
+    <row r="8" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>128</v>
       </c>
@@ -5133,7 +5133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:151">
+    <row r="9" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>129</v>
       </c>
@@ -5581,7 +5581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:151">
+    <row r="10" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>129</v>
       </c>
@@ -6029,7 +6029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:151">
+    <row r="11" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>129</v>
       </c>
@@ -6477,7 +6477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:151">
+    <row r="12" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>129</v>
       </c>
@@ -6925,7 +6925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:151">
+    <row r="13" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>129</v>
       </c>
@@ -7373,7 +7373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:151">
+    <row r="14" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>129</v>
       </c>
@@ -7821,7 +7821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:151">
+    <row r="15" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>129</v>
       </c>
@@ -8268,7 +8268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:151">
+    <row r="16" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>130</v>
       </c>
@@ -8715,7 +8715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:150">
+    <row r="17" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>130</v>
       </c>
@@ -9163,7 +9163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:150">
+    <row r="18" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>130</v>
       </c>
@@ -9611,7 +9611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:150">
+    <row r="19" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>130</v>
       </c>
@@ -10059,7 +10059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:150">
+    <row r="20" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>130</v>
       </c>
@@ -10506,7 +10506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:150">
+    <row r="21" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>130</v>
       </c>
@@ -10953,7 +10953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:150">
+    <row r="22" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>130</v>
       </c>
@@ -11400,7 +11400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:150">
+    <row r="23" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>133</v>
       </c>
@@ -11848,7 +11848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:150">
+    <row r="24" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>133</v>
       </c>
@@ -12296,7 +12296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:150">
+    <row r="25" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>133</v>
       </c>
@@ -12744,7 +12744,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="26" spans="1:150">
+    <row r="26" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>133</v>
       </c>
@@ -13192,7 +13192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:150">
+    <row r="27" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>133</v>
       </c>
@@ -13640,7 +13640,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="28" spans="1:150">
+    <row r="28" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>133</v>
       </c>
@@ -13651,7 +13651,7 @@
         <v>45265</v>
       </c>
       <c r="D28" s="6"/>
-      <c r="E28" s="10">
+      <c r="E28">
         <v>-999</v>
       </c>
       <c r="F28" s="6">
@@ -14087,7 +14087,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="29" spans="1:150">
+    <row r="29" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>133</v>
       </c>
@@ -14098,7 +14098,7 @@
         <v>45266</v>
       </c>
       <c r="D29" s="6"/>
-      <c r="E29" s="10">
+      <c r="E29">
         <v>-999</v>
       </c>
       <c r="F29" s="6">
@@ -14534,7 +14534,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="30" spans="1:150">
+    <row r="30" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>134</v>
       </c>
@@ -14981,7 +14981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:150">
+    <row r="31" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>134</v>
       </c>
@@ -15428,7 +15428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:150">
+    <row r="32" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>134</v>
       </c>
@@ -15876,7 +15876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:150">
+    <row r="33" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>134</v>
       </c>
@@ -15887,7 +15887,7 @@
         <v>44963</v>
       </c>
       <c r="D33" s="6"/>
-      <c r="E33" s="10">
+      <c r="E33">
         <v>-999</v>
       </c>
       <c r="F33" s="6">
@@ -16324,7 +16324,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="34" spans="1:150">
+    <row r="34" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>134</v>
       </c>
@@ -16335,7 +16335,7 @@
         <v>44964</v>
       </c>
       <c r="D34" s="6"/>
-      <c r="E34" s="10">
+      <c r="E34">
         <v>-999</v>
       </c>
       <c r="F34" s="6">
@@ -16772,7 +16772,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="35" spans="1:150">
+    <row r="35" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>134</v>
       </c>
@@ -16783,7 +16783,7 @@
         <v>44965</v>
       </c>
       <c r="D35" s="6"/>
-      <c r="E35" s="10">
+      <c r="E35">
         <v>-999</v>
       </c>
       <c r="F35" s="6">
@@ -17220,7 +17220,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="36" spans="1:150">
+    <row r="36" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>134</v>
       </c>
@@ -17231,7 +17231,7 @@
         <v>44966</v>
       </c>
       <c r="D36" s="6"/>
-      <c r="E36" s="10">
+      <c r="E36">
         <v>-999</v>
       </c>
       <c r="F36" s="6">
@@ -17668,7 +17668,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="37" spans="1:150">
+    <row r="37" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>135</v>
       </c>
@@ -17679,7 +17679,7 @@
         <v>45358</v>
       </c>
       <c r="D37" s="6"/>
-      <c r="E37" s="10">
+      <c r="E37">
         <v>-999</v>
       </c>
       <c r="F37" s="6">
@@ -18116,7 +18116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:150">
+    <row r="38" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>135</v>
       </c>
@@ -18564,7 +18564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:150">
+    <row r="39" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>135</v>
       </c>
@@ -19011,7 +19011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:150">
+    <row r="40" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>135</v>
       </c>
@@ -19459,7 +19459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:150">
+    <row r="41" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>135</v>
       </c>
@@ -19907,7 +19907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:150">
+    <row r="42" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>135</v>
       </c>
@@ -20355,7 +20355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:150">
+    <row r="43" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>135</v>
       </c>
@@ -20803,7 +20803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:150">
+    <row r="44" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>136</v>
       </c>
@@ -21251,7 +21251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:150">
+    <row r="45" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>136</v>
       </c>
@@ -21699,7 +21699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:150">
+    <row r="46" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>136</v>
       </c>
@@ -22147,7 +22147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:150">
+    <row r="47" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>136</v>
       </c>
@@ -22594,7 +22594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:150">
+    <row r="48" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>136</v>
       </c>
@@ -23042,7 +23042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:150">
+    <row r="49" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>136</v>
       </c>
@@ -23489,7 +23489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:150">
+    <row r="50" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>136</v>
       </c>
@@ -23937,7 +23937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:150">
+    <row r="51" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>139</v>
       </c>
@@ -24385,7 +24385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:150">
+    <row r="52" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>139</v>
       </c>
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:150">
+    <row r="53" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>139</v>
       </c>
@@ -25281,7 +25281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:150">
+    <row r="54" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>139</v>
       </c>
@@ -25726,7 +25726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:150">
+    <row r="55" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>139</v>
       </c>
@@ -26174,7 +26174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:150">
+    <row r="56" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>139</v>
       </c>
@@ -26622,7 +26622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:150">
+    <row r="57" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>139</v>
       </c>
@@ -27069,7 +27069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:150">
+    <row r="58" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>140</v>
       </c>
@@ -27517,7 +27517,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="59" spans="1:150">
+    <row r="59" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>140</v>
       </c>
@@ -27965,7 +27965,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="60" spans="1:150">
+    <row r="60" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>140</v>
       </c>
@@ -28413,7 +28413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:150">
+    <row r="61" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>140</v>
       </c>
@@ -28860,7 +28860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:150">
+    <row r="62" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>140</v>
       </c>
@@ -29308,7 +29308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:150">
+    <row r="63" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>140</v>
       </c>
@@ -29756,7 +29756,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="64" spans="1:150">
+    <row r="64" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>140</v>
       </c>
@@ -30204,7 +30204,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="65" spans="1:150">
+    <row r="65" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>141</v>
       </c>
@@ -30652,7 +30652,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="66" spans="1:150">
+    <row r="66" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>141</v>
       </c>
@@ -31100,7 +31100,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="67" spans="1:150">
+    <row r="67" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>141</v>
       </c>
@@ -31548,7 +31548,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="68" spans="1:150">
+    <row r="68" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>141</v>
       </c>
@@ -31996,7 +31996,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="69" spans="1:150">
+    <row r="69" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>141</v>
       </c>
@@ -32444,7 +32444,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="70" spans="1:150">
+    <row r="70" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>141</v>
       </c>
@@ -32892,7 +32892,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="71" spans="1:150">
+    <row r="71" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>141</v>
       </c>
@@ -33340,7 +33340,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="72" spans="1:150">
+    <row r="72" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>142</v>
       </c>
@@ -33788,7 +33788,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="73" spans="1:150">
+    <row r="73" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>142</v>
       </c>
@@ -34236,7 +34236,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="74" spans="1:150">
+    <row r="74" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>142</v>
       </c>
@@ -34684,7 +34684,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="75" spans="1:150">
+    <row r="75" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>142</v>
       </c>
@@ -35132,7 +35132,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="76" spans="1:150">
+    <row r="76" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>142</v>
       </c>
@@ -35580,7 +35580,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="77" spans="1:150">
+    <row r="77" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>142</v>
       </c>
@@ -36028,7 +36028,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="78" spans="1:150">
+    <row r="78" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>142</v>
       </c>
@@ -36476,7 +36476,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="79" spans="1:150">
+    <row r="79" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>143</v>
       </c>
@@ -36924,7 +36924,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="80" spans="1:150">
+    <row r="80" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>143</v>
       </c>
@@ -37371,7 +37371,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="81" spans="1:150">
+    <row r="81" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>143</v>
       </c>
@@ -37818,7 +37818,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="82" spans="1:150">
+    <row r="82" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>143</v>
       </c>
@@ -38266,7 +38266,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="83" spans="1:150">
+    <row r="83" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>143</v>
       </c>
@@ -38714,7 +38714,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="84" spans="1:150">
+    <row r="84" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>143</v>
       </c>
@@ -39161,7 +39161,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="85" spans="1:150">
+    <row r="85" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>143</v>
       </c>
@@ -39608,7 +39608,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="86" spans="1:150">
+    <row r="86" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>144</v>
       </c>
@@ -40056,7 +40056,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="87" spans="1:150">
+    <row r="87" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>144</v>
       </c>
@@ -40504,7 +40504,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="88" spans="1:150">
+    <row r="88" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>144</v>
       </c>
@@ -40952,7 +40952,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="89" spans="1:150">
+    <row r="89" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>144</v>
       </c>
@@ -41400,7 +41400,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="90" spans="1:150">
+    <row r="90" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>144</v>
       </c>
@@ -41848,7 +41848,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="91" spans="1:150">
+    <row r="91" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>144</v>
       </c>
@@ -42296,7 +42296,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="92" spans="1:150">
+    <row r="92" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>144</v>
       </c>
@@ -42744,7 +42744,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="93" spans="1:150">
+    <row r="93" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>145</v>
       </c>
@@ -43192,7 +43192,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="94" spans="1:150">
+    <row r="94" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>145</v>
       </c>
@@ -43640,7 +43640,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="95" spans="1:150">
+    <row r="95" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>145</v>
       </c>
@@ -44088,7 +44088,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="96" spans="1:150">
+    <row r="96" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>145</v>
       </c>
@@ -44536,7 +44536,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="97" spans="1:150">
+    <row r="97" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>145</v>
       </c>
@@ -44984,7 +44984,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="98" spans="1:150">
+    <row r="98" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>145</v>
       </c>
@@ -45432,7 +45432,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="99" spans="1:150">
+    <row r="99" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>145</v>
       </c>
@@ -45880,7 +45880,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="100" spans="1:150">
+    <row r="100" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>146</v>
       </c>
@@ -46328,7 +46328,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="101" spans="1:150">
+    <row r="101" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>146</v>
       </c>
@@ -46776,7 +46776,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="102" spans="1:150">
+    <row r="102" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>146</v>
       </c>
@@ -47224,7 +47224,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="103" spans="1:150">
+    <row r="103" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>146</v>
       </c>
@@ -47672,7 +47672,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="104" spans="1:150">
+    <row r="104" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>146</v>
       </c>
@@ -48120,7 +48120,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="105" spans="1:150">
+    <row r="105" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>146</v>
       </c>
@@ -48568,7 +48568,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="106" spans="1:150">
+    <row r="106" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>146</v>
       </c>
@@ -49016,7 +49016,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="107" spans="1:150">
+    <row r="107" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>148</v>
       </c>
@@ -49463,7 +49463,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="108" spans="1:150">
+    <row r="108" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>148</v>
       </c>
@@ -49911,7 +49911,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="109" spans="1:150">
+    <row r="109" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>148</v>
       </c>
@@ -50359,7 +50359,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="110" spans="1:150">
+    <row r="110" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>148</v>
       </c>
@@ -50370,7 +50370,7 @@
         <v>45404</v>
       </c>
       <c r="D110" s="6"/>
-      <c r="E110" s="10">
+      <c r="E110">
         <v>-999</v>
       </c>
       <c r="F110" s="6">
@@ -50807,7 +50807,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="111" spans="1:150">
+    <row r="111" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>148</v>
       </c>
@@ -50818,7 +50818,7 @@
         <v>45405</v>
       </c>
       <c r="D111" s="6"/>
-      <c r="E111" s="10">
+      <c r="E111">
         <v>-999</v>
       </c>
       <c r="F111" s="6">
@@ -51255,7 +51255,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="112" spans="1:150">
+    <row r="112" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>148</v>
       </c>
@@ -51703,7 +51703,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="113" spans="1:150">
+    <row r="113" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>148</v>
       </c>
@@ -52150,7 +52150,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="114" spans="1:150">
+    <row r="114" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>151</v>
       </c>
@@ -52598,7 +52598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:150">
+    <row r="115" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>151</v>
       </c>
@@ -53045,7 +53045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:150">
+    <row r="116" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>151</v>
       </c>
@@ -53492,7 +53492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:150">
+    <row r="117" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>151</v>
       </c>
@@ -53939,7 +53939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:150">
+    <row r="118" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>151</v>
       </c>
@@ -54387,7 +54387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:150">
+    <row r="119" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>151</v>
       </c>
@@ -54835,7 +54835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:150">
+    <row r="120" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>151</v>
       </c>
@@ -55283,7 +55283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:150">
+    <row r="121" spans="1:150" x14ac:dyDescent="0.2">
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
@@ -55302,7 +55302,7 @@
       <c r="AZ121" s="5"/>
       <c r="BB121" s="6"/>
     </row>
-    <row r="122" spans="1:150">
+    <row r="122" spans="1:150" x14ac:dyDescent="0.2">
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
@@ -55322,7 +55322,7 @@
       <c r="AZ122" s="5"/>
       <c r="BB122" s="6"/>
     </row>
-    <row r="123" spans="1:150">
+    <row r="123" spans="1:150" x14ac:dyDescent="0.2">
       <c r="G123" s="5"/>
       <c r="H123" s="5"/>
       <c r="J123" s="5"/>
@@ -55336,7 +55336,7 @@
       <c r="AZ123" s="5"/>
       <c r="BB123" s="6"/>
     </row>
-    <row r="124" spans="1:150">
+    <row r="124" spans="1:150" x14ac:dyDescent="0.2">
       <c r="C124" s="1"/>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
@@ -55355,7 +55355,7 @@
       <c r="AZ124" s="5"/>
       <c r="BB124" s="6"/>
     </row>
-    <row r="125" spans="1:150">
+    <row r="125" spans="1:150" x14ac:dyDescent="0.2">
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
@@ -55374,7 +55374,7 @@
       <c r="AZ125" s="5"/>
       <c r="BB125" s="6"/>
     </row>
-    <row r="126" spans="1:150">
+    <row r="126" spans="1:150" x14ac:dyDescent="0.2">
       <c r="G126" s="5"/>
       <c r="H126" s="5"/>
       <c r="J126" s="5"/>
@@ -55388,7 +55388,7 @@
       <c r="AZ126" s="5"/>
       <c r="BB126" s="6"/>
     </row>
-    <row r="127" spans="1:150">
+    <row r="127" spans="1:150" x14ac:dyDescent="0.2">
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
@@ -55408,7 +55408,7 @@
       <c r="AZ127" s="5"/>
       <c r="BB127" s="6"/>
     </row>
-    <row r="128" spans="1:150">
+    <row r="128" spans="1:150" x14ac:dyDescent="0.2">
       <c r="G128" s="5"/>
       <c r="H128" s="5"/>
       <c r="J128" s="5"/>
@@ -55423,7 +55423,7 @@
       <c r="AZ128" s="5"/>
       <c r="BB128" s="6"/>
     </row>
-    <row r="129" spans="3:59">
+    <row r="129" spans="3:59" x14ac:dyDescent="0.2">
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
@@ -55443,7 +55443,7 @@
       <c r="AZ129" s="5"/>
       <c r="BB129" s="6"/>
     </row>
-    <row r="130" spans="3:59">
+    <row r="130" spans="3:59" x14ac:dyDescent="0.2">
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
@@ -55463,7 +55463,7 @@
       <c r="AZ130" s="5"/>
       <c r="BB130" s="6"/>
     </row>
-    <row r="131" spans="3:59">
+    <row r="131" spans="3:59" x14ac:dyDescent="0.2">
       <c r="C131" s="1"/>
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
@@ -55483,7 +55483,7 @@
       <c r="AZ131" s="5"/>
       <c r="BB131" s="6"/>
     </row>
-    <row r="132" spans="3:59">
+    <row r="132" spans="3:59" x14ac:dyDescent="0.2">
       <c r="G132" s="5"/>
       <c r="H132" s="5"/>
       <c r="J132" s="5"/>
@@ -55498,7 +55498,7 @@
       <c r="AZ132" s="5"/>
       <c r="BB132" s="6"/>
     </row>
-    <row r="133" spans="3:59">
+    <row r="133" spans="3:59" x14ac:dyDescent="0.2">
       <c r="C133" s="1"/>
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
@@ -55517,7 +55517,7 @@
       <c r="AZ133" s="5"/>
       <c r="BB133" s="6"/>
     </row>
-    <row r="134" spans="3:59">
+    <row r="134" spans="3:59" x14ac:dyDescent="0.2">
       <c r="G134" s="5"/>
       <c r="H134" s="5"/>
       <c r="J134" s="5"/>
@@ -55531,7 +55531,7 @@
       <c r="AZ134" s="5"/>
       <c r="BB134" s="6"/>
     </row>
-    <row r="135" spans="3:59">
+    <row r="135" spans="3:59" x14ac:dyDescent="0.2">
       <c r="G135" s="5"/>
       <c r="H135" s="5"/>
       <c r="J135" s="5"/>
@@ -55545,7 +55545,7 @@
       <c r="AZ135" s="5"/>
       <c r="BB135" s="6"/>
     </row>
-    <row r="136" spans="3:59">
+    <row r="136" spans="3:59" x14ac:dyDescent="0.2">
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
@@ -55565,7 +55565,7 @@
       <c r="BB136" s="6"/>
       <c r="BE136" s="3"/>
     </row>
-    <row r="137" spans="3:59">
+    <row r="137" spans="3:59" x14ac:dyDescent="0.2">
       <c r="G137" s="5"/>
       <c r="H137" s="5"/>
       <c r="J137" s="5"/>
@@ -55581,7 +55581,7 @@
       <c r="BE137" s="3"/>
       <c r="BG137" s="3"/>
     </row>
-    <row r="138" spans="3:59">
+    <row r="138" spans="3:59" x14ac:dyDescent="0.2">
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
@@ -55601,7 +55601,7 @@
       <c r="AZ138" s="5"/>
       <c r="BB138" s="6"/>
     </row>
-    <row r="139" spans="3:59">
+    <row r="139" spans="3:59" x14ac:dyDescent="0.2">
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
@@ -55621,7 +55621,7 @@
       <c r="BB139" s="6"/>
       <c r="BE139" s="3"/>
     </row>
-    <row r="140" spans="3:59">
+    <row r="140" spans="3:59" x14ac:dyDescent="0.2">
       <c r="C140" s="1"/>
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
@@ -55641,7 +55641,7 @@
       <c r="AZ140" s="5"/>
       <c r="BB140" s="6"/>
     </row>
-    <row r="141" spans="3:59">
+    <row r="141" spans="3:59" x14ac:dyDescent="0.2">
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
@@ -55660,7 +55660,7 @@
       <c r="AZ141" s="5"/>
       <c r="BB141" s="6"/>
     </row>
-    <row r="142" spans="3:59">
+    <row r="142" spans="3:59" x14ac:dyDescent="0.2">
       <c r="G142" s="5"/>
       <c r="H142" s="5"/>
       <c r="J142" s="5"/>
@@ -55674,7 +55674,7 @@
       <c r="AZ142" s="5"/>
       <c r="BB142" s="6"/>
     </row>
-    <row r="143" spans="3:59">
+    <row r="143" spans="3:59" x14ac:dyDescent="0.2">
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
       <c r="J143" s="5"/>
@@ -55688,7 +55688,7 @@
       <c r="AZ143" s="5"/>
       <c r="BB143" s="6"/>
     </row>
-    <row r="144" spans="3:59">
+    <row r="144" spans="3:59" x14ac:dyDescent="0.2">
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
@@ -55708,7 +55708,7 @@
       <c r="AZ144" s="5"/>
       <c r="BB144" s="6"/>
     </row>
-    <row r="145" spans="3:89">
+    <row r="145" spans="3:89" x14ac:dyDescent="0.2">
       <c r="C145" s="1"/>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
@@ -55728,7 +55728,7 @@
       <c r="AZ145" s="5"/>
       <c r="BB145" s="6"/>
     </row>
-    <row r="146" spans="3:89">
+    <row r="146" spans="3:89" x14ac:dyDescent="0.2">
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
@@ -55748,7 +55748,7 @@
       <c r="AZ146" s="5"/>
       <c r="BB146" s="6"/>
     </row>
-    <row r="147" spans="3:89">
+    <row r="147" spans="3:89" x14ac:dyDescent="0.2">
       <c r="C147" s="1"/>
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
@@ -55768,7 +55768,7 @@
       <c r="AZ147" s="5"/>
       <c r="BB147" s="6"/>
     </row>
-    <row r="148" spans="3:89">
+    <row r="148" spans="3:89" x14ac:dyDescent="0.2">
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
@@ -55789,7 +55789,7 @@
       <c r="AZ148" s="5"/>
       <c r="BB148" s="6"/>
     </row>
-    <row r="149" spans="3:89">
+    <row r="149" spans="3:89" x14ac:dyDescent="0.2">
       <c r="C149" s="1"/>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
@@ -55809,7 +55809,7 @@
       <c r="AZ149" s="5"/>
       <c r="BB149" s="6"/>
     </row>
-    <row r="150" spans="3:89">
+    <row r="150" spans="3:89" x14ac:dyDescent="0.2">
       <c r="C150" s="1"/>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
@@ -55829,7 +55829,7 @@
       <c r="AZ150" s="5"/>
       <c r="BB150" s="6"/>
     </row>
-    <row r="151" spans="3:89">
+    <row r="151" spans="3:89" x14ac:dyDescent="0.2">
       <c r="G151" s="5"/>
       <c r="H151" s="5"/>
       <c r="J151" s="5"/>
@@ -55843,7 +55843,7 @@
       <c r="AZ151" s="5"/>
       <c r="BB151" s="6"/>
     </row>
-    <row r="152" spans="3:89">
+    <row r="152" spans="3:89" x14ac:dyDescent="0.2">
       <c r="C152" s="1"/>
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
@@ -55866,7 +55866,7 @@
       <c r="CH152" s="3"/>
       <c r="CK152" s="3"/>
     </row>
-    <row r="153" spans="3:89">
+    <row r="153" spans="3:89" x14ac:dyDescent="0.2">
       <c r="C153" s="1"/>
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
@@ -55887,7 +55887,7 @@
       <c r="BB153" s="6"/>
       <c r="BE153" s="3"/>
     </row>
-    <row r="154" spans="3:89">
+    <row r="154" spans="3:89" x14ac:dyDescent="0.2">
       <c r="C154" s="1"/>
       <c r="D154" s="1"/>
       <c r="E154" s="1"/>
@@ -55908,7 +55908,7 @@
       <c r="AZ154" s="5"/>
       <c r="BB154" s="6"/>
     </row>
-    <row r="155" spans="3:89">
+    <row r="155" spans="3:89" x14ac:dyDescent="0.2">
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
       <c r="E155" s="1"/>
@@ -55927,7 +55927,7 @@
       <c r="AZ155" s="5"/>
       <c r="BB155" s="6"/>
     </row>
-    <row r="156" spans="3:89">
+    <row r="156" spans="3:89" x14ac:dyDescent="0.2">
       <c r="C156" s="1"/>
       <c r="D156" s="1"/>
       <c r="E156" s="1"/>
@@ -55948,7 +55948,7 @@
       <c r="BB156" s="6"/>
       <c r="BE156" s="3"/>
     </row>
-    <row r="157" spans="3:89">
+    <row r="157" spans="3:89" x14ac:dyDescent="0.2">
       <c r="C157" s="1"/>
       <c r="D157" s="1"/>
       <c r="E157" s="1"/>
@@ -55969,7 +55969,7 @@
       <c r="AZ157" s="5"/>
       <c r="BB157" s="6"/>
     </row>
-    <row r="158" spans="3:89">
+    <row r="158" spans="3:89" x14ac:dyDescent="0.2">
       <c r="C158" s="1"/>
       <c r="D158" s="1"/>
       <c r="E158" s="1"/>
@@ -55989,7 +55989,7 @@
       <c r="AZ158" s="5"/>
       <c r="BB158" s="6"/>
     </row>
-    <row r="159" spans="3:89">
+    <row r="159" spans="3:89" x14ac:dyDescent="0.2">
       <c r="G159" s="5"/>
       <c r="H159" s="5"/>
       <c r="J159" s="5"/>
@@ -56003,7 +56003,7 @@
       <c r="AZ159" s="5"/>
       <c r="BB159" s="6"/>
     </row>
-    <row r="160" spans="3:89">
+    <row r="160" spans="3:89" x14ac:dyDescent="0.2">
       <c r="G160" s="5"/>
       <c r="H160" s="5"/>
       <c r="J160" s="5"/>
@@ -56018,7 +56018,7 @@
       <c r="AZ160" s="5"/>
       <c r="BB160" s="6"/>
     </row>
-    <row r="161" spans="3:86">
+    <row r="161" spans="3:86" x14ac:dyDescent="0.2">
       <c r="G161" s="5"/>
       <c r="H161" s="5"/>
       <c r="J161" s="5"/>
@@ -56032,7 +56032,7 @@
       <c r="AZ161" s="5"/>
       <c r="BB161" s="6"/>
     </row>
-    <row r="162" spans="3:86">
+    <row r="162" spans="3:86" x14ac:dyDescent="0.2">
       <c r="G162" s="5"/>
       <c r="H162" s="5"/>
       <c r="J162" s="5"/>
@@ -56046,7 +56046,7 @@
       <c r="AZ162" s="5"/>
       <c r="BB162" s="6"/>
     </row>
-    <row r="163" spans="3:86">
+    <row r="163" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C163" s="1"/>
       <c r="D163" s="1"/>
       <c r="E163" s="1"/>
@@ -56065,7 +56065,7 @@
       <c r="AZ163" s="5"/>
       <c r="BB163" s="6"/>
     </row>
-    <row r="164" spans="3:86">
+    <row r="164" spans="3:86" x14ac:dyDescent="0.2">
       <c r="G164" s="5"/>
       <c r="H164" s="5"/>
       <c r="J164" s="5"/>
@@ -56080,7 +56080,7 @@
       <c r="AZ164" s="5"/>
       <c r="BB164" s="6"/>
     </row>
-    <row r="165" spans="3:86">
+    <row r="165" spans="3:86" x14ac:dyDescent="0.2">
       <c r="G165" s="5"/>
       <c r="H165" s="5"/>
       <c r="J165" s="5"/>
@@ -56095,7 +56095,7 @@
       <c r="AZ165" s="5"/>
       <c r="BB165" s="6"/>
     </row>
-    <row r="166" spans="3:86">
+    <row r="166" spans="3:86" x14ac:dyDescent="0.2">
       <c r="G166" s="5"/>
       <c r="H166" s="5"/>
       <c r="J166" s="5"/>
@@ -56110,7 +56110,7 @@
       <c r="AZ166" s="5"/>
       <c r="BB166" s="6"/>
     </row>
-    <row r="167" spans="3:86">
+    <row r="167" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
       <c r="E167" s="1"/>
@@ -56129,7 +56129,7 @@
       <c r="AZ167" s="5"/>
       <c r="BB167" s="6"/>
     </row>
-    <row r="168" spans="3:86">
+    <row r="168" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
       <c r="E168" s="1"/>
@@ -56148,7 +56148,7 @@
       <c r="AX168" s="5"/>
       <c r="BB168" s="6"/>
     </row>
-    <row r="169" spans="3:86">
+    <row r="169" spans="3:86" x14ac:dyDescent="0.2">
       <c r="G169" s="5"/>
       <c r="H169" s="5"/>
       <c r="J169" s="5"/>
@@ -56161,7 +56161,7 @@
       <c r="AX169" s="5"/>
       <c r="BB169" s="6"/>
     </row>
-    <row r="170" spans="3:86">
+    <row r="170" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C170" s="1"/>
       <c r="D170" s="1"/>
       <c r="E170" s="1"/>
@@ -56179,7 +56179,7 @@
       <c r="AX170" s="5"/>
       <c r="BB170" s="6"/>
     </row>
-    <row r="171" spans="3:86">
+    <row r="171" spans="3:86" x14ac:dyDescent="0.2">
       <c r="G171" s="5"/>
       <c r="H171" s="5"/>
       <c r="J171" s="5"/>
@@ -56193,7 +56193,7 @@
       <c r="AX171" s="5"/>
       <c r="BB171" s="6"/>
     </row>
-    <row r="172" spans="3:86">
+    <row r="172" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C172" s="1"/>
       <c r="D172" s="1"/>
       <c r="E172" s="1"/>
@@ -56211,7 +56211,7 @@
       <c r="AX172" s="5"/>
       <c r="BB172" s="6"/>
     </row>
-    <row r="173" spans="3:86">
+    <row r="173" spans="3:86" x14ac:dyDescent="0.2">
       <c r="G173" s="5"/>
       <c r="H173" s="5"/>
       <c r="J173" s="5"/>
@@ -56224,7 +56224,7 @@
       <c r="AX173" s="5"/>
       <c r="BB173" s="6"/>
     </row>
-    <row r="174" spans="3:86">
+    <row r="174" spans="3:86" x14ac:dyDescent="0.2">
       <c r="G174" s="5"/>
       <c r="H174" s="5"/>
       <c r="J174" s="5"/>
@@ -56239,7 +56239,7 @@
       <c r="BB174" s="6"/>
       <c r="CH174" s="3"/>
     </row>
-    <row r="175" spans="3:86">
+    <row r="175" spans="3:86" x14ac:dyDescent="0.2">
       <c r="G175" s="5"/>
       <c r="H175" s="5"/>
       <c r="J175" s="5"/>
@@ -56252,7 +56252,7 @@
       <c r="AX175" s="5"/>
       <c r="BB175" s="6"/>
     </row>
-    <row r="176" spans="3:86">
+    <row r="176" spans="3:86" x14ac:dyDescent="0.2">
       <c r="G176" s="5"/>
       <c r="H176" s="5"/>
       <c r="J176" s="5"/>
@@ -56265,7 +56265,7 @@
       <c r="AX176" s="5"/>
       <c r="BB176" s="6"/>
     </row>
-    <row r="177" spans="3:59">
+    <row r="177" spans="3:59" x14ac:dyDescent="0.2">
       <c r="G177" s="5"/>
       <c r="H177" s="5"/>
       <c r="J177" s="5"/>
@@ -56279,7 +56279,7 @@
       <c r="AX177" s="5"/>
       <c r="BB177" s="6"/>
     </row>
-    <row r="178" spans="3:59">
+    <row r="178" spans="3:59" x14ac:dyDescent="0.2">
       <c r="G178" s="5"/>
       <c r="H178" s="5"/>
       <c r="J178" s="5"/>
@@ -56292,7 +56292,7 @@
       <c r="AX178" s="5"/>
       <c r="BB178" s="6"/>
     </row>
-    <row r="179" spans="3:59">
+    <row r="179" spans="3:59" x14ac:dyDescent="0.2">
       <c r="C179" s="1"/>
       <c r="D179" s="1"/>
       <c r="E179" s="1"/>
@@ -56310,7 +56310,7 @@
       <c r="AX179" s="5"/>
       <c r="BB179" s="6"/>
     </row>
-    <row r="180" spans="3:59">
+    <row r="180" spans="3:59" x14ac:dyDescent="0.2">
       <c r="C180" s="1"/>
       <c r="D180" s="1"/>
       <c r="E180" s="1"/>
@@ -56328,7 +56328,7 @@
       <c r="AX180" s="5"/>
       <c r="BB180" s="6"/>
     </row>
-    <row r="181" spans="3:59">
+    <row r="181" spans="3:59" x14ac:dyDescent="0.2">
       <c r="G181" s="5"/>
       <c r="H181" s="5"/>
       <c r="J181" s="5"/>
@@ -56342,7 +56342,7 @@
       <c r="AX181" s="5"/>
       <c r="BB181" s="6"/>
     </row>
-    <row r="182" spans="3:59">
+    <row r="182" spans="3:59" x14ac:dyDescent="0.2">
       <c r="C182" s="1"/>
       <c r="D182" s="1"/>
       <c r="E182" s="1"/>
@@ -56361,7 +56361,7 @@
       <c r="AX182" s="5"/>
       <c r="BB182" s="6"/>
     </row>
-    <row r="183" spans="3:59">
+    <row r="183" spans="3:59" x14ac:dyDescent="0.2">
       <c r="C183" s="1"/>
       <c r="D183" s="1"/>
       <c r="E183" s="1"/>
@@ -56378,7 +56378,7 @@
       <c r="AX183" s="5"/>
       <c r="BB183" s="6"/>
     </row>
-    <row r="184" spans="3:59">
+    <row r="184" spans="3:59" x14ac:dyDescent="0.2">
       <c r="C184" s="1"/>
       <c r="D184" s="1"/>
       <c r="E184" s="1"/>
@@ -56394,7 +56394,7 @@
       <c r="AX184" s="5"/>
       <c r="BB184" s="6"/>
     </row>
-    <row r="185" spans="3:59">
+    <row r="185" spans="3:59" x14ac:dyDescent="0.2">
       <c r="G185" s="5"/>
       <c r="J185" s="5"/>
       <c r="K185" s="6"/>
@@ -56406,7 +56406,7 @@
       <c r="AX185" s="5"/>
       <c r="BB185" s="6"/>
     </row>
-    <row r="186" spans="3:59">
+    <row r="186" spans="3:59" x14ac:dyDescent="0.2">
       <c r="G186" s="5"/>
       <c r="J186" s="5"/>
       <c r="K186" s="6"/>
@@ -56417,7 +56417,7 @@
       <c r="AX186" s="5"/>
       <c r="BB186" s="6"/>
     </row>
-    <row r="187" spans="3:59">
+    <row r="187" spans="3:59" x14ac:dyDescent="0.2">
       <c r="C187" s="1"/>
       <c r="D187" s="1"/>
       <c r="E187" s="1"/>
@@ -56435,7 +56435,7 @@
       <c r="BB187" s="6"/>
       <c r="BE187" s="3"/>
     </row>
-    <row r="188" spans="3:59">
+    <row r="188" spans="3:59" x14ac:dyDescent="0.2">
       <c r="C188" s="1"/>
       <c r="D188" s="1"/>
       <c r="E188" s="1"/>
@@ -56454,7 +56454,7 @@
       <c r="BB188" s="6"/>
       <c r="BE188" s="3"/>
     </row>
-    <row r="189" spans="3:59">
+    <row r="189" spans="3:59" x14ac:dyDescent="0.2">
       <c r="C189" s="1"/>
       <c r="D189" s="1"/>
       <c r="E189" s="1"/>
@@ -56473,7 +56473,7 @@
       <c r="BB189" s="6"/>
       <c r="BE189" s="3"/>
     </row>
-    <row r="190" spans="3:59">
+    <row r="190" spans="3:59" x14ac:dyDescent="0.2">
       <c r="C190" s="1"/>
       <c r="D190" s="1"/>
       <c r="E190" s="1"/>
@@ -56491,7 +56491,7 @@
       <c r="AY190" s="3"/>
       <c r="BB190" s="6"/>
     </row>
-    <row r="191" spans="3:59">
+    <row r="191" spans="3:59" x14ac:dyDescent="0.2">
       <c r="J191" s="5"/>
       <c r="K191" s="6"/>
       <c r="L191" s="6"/>
@@ -56505,7 +56505,7 @@
       <c r="BE191" s="3"/>
       <c r="BG191" s="3"/>
     </row>
-    <row r="192" spans="3:59">
+    <row r="192" spans="3:59" x14ac:dyDescent="0.2">
       <c r="C192" s="1"/>
       <c r="D192" s="1"/>
       <c r="E192" s="1"/>
@@ -56523,7 +56523,7 @@
       <c r="AY192" s="3"/>
       <c r="BB192" s="6"/>
     </row>
-    <row r="193" spans="3:95">
+    <row r="193" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C193" s="1"/>
       <c r="D193" s="1"/>
       <c r="E193" s="1"/>
@@ -56540,7 +56540,7 @@
       <c r="AX193" s="5"/>
       <c r="BB193" s="6"/>
     </row>
-    <row r="194" spans="3:95">
+    <row r="194" spans="3:95" x14ac:dyDescent="0.2">
       <c r="J194" s="5"/>
       <c r="K194" s="6"/>
       <c r="L194" s="6"/>
@@ -56550,7 +56550,7 @@
       <c r="AX194" s="5"/>
       <c r="BB194" s="6"/>
     </row>
-    <row r="195" spans="3:95">
+    <row r="195" spans="3:95" x14ac:dyDescent="0.2">
       <c r="J195" s="5"/>
       <c r="K195" s="6"/>
       <c r="L195" s="6"/>
@@ -56560,7 +56560,7 @@
       <c r="AX195" s="5"/>
       <c r="BB195" s="6"/>
     </row>
-    <row r="196" spans="3:95">
+    <row r="196" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C196" s="1"/>
       <c r="D196" s="1"/>
       <c r="E196" s="1"/>
@@ -56578,7 +56578,7 @@
       <c r="AY196" s="3"/>
       <c r="BB196" s="6"/>
     </row>
-    <row r="197" spans="3:95">
+    <row r="197" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C197" s="1"/>
       <c r="D197" s="1"/>
       <c r="E197" s="1"/>
@@ -56595,7 +56595,7 @@
       <c r="AX197" s="5"/>
       <c r="BB197" s="6"/>
     </row>
-    <row r="198" spans="3:95">
+    <row r="198" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C198" s="1"/>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
@@ -56612,7 +56612,7 @@
       <c r="AX198" s="5"/>
       <c r="BB198" s="6"/>
     </row>
-    <row r="199" spans="3:95">
+    <row r="199" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C199" s="1"/>
       <c r="D199" s="1"/>
       <c r="E199" s="1"/>
@@ -56630,7 +56630,7 @@
       <c r="AY199" s="3"/>
       <c r="BB199" s="6"/>
     </row>
-    <row r="200" spans="3:95">
+    <row r="200" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="E200" s="1"/>
@@ -56647,7 +56647,7 @@
       <c r="AX200" s="5"/>
       <c r="BB200" s="6"/>
     </row>
-    <row r="201" spans="3:95">
+    <row r="201" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C201" s="1"/>
       <c r="D201" s="1"/>
       <c r="E201" s="1"/>
@@ -56664,7 +56664,7 @@
       <c r="AX201" s="5"/>
       <c r="BB201" s="6"/>
     </row>
-    <row r="202" spans="3:95">
+    <row r="202" spans="3:95" x14ac:dyDescent="0.2">
       <c r="J202" s="5"/>
       <c r="K202" s="6"/>
       <c r="L202" s="6"/>
@@ -56674,7 +56674,7 @@
       <c r="AX202" s="5"/>
       <c r="BB202" s="6"/>
     </row>
-    <row r="203" spans="3:95">
+    <row r="203" spans="3:95" x14ac:dyDescent="0.2">
       <c r="J203" s="5"/>
       <c r="K203" s="6"/>
       <c r="L203" s="6"/>
@@ -56684,7 +56684,7 @@
       <c r="AX203" s="5"/>
       <c r="BB203" s="6"/>
     </row>
-    <row r="204" spans="3:95">
+    <row r="204" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C204" s="1"/>
       <c r="D204" s="1"/>
       <c r="E204" s="1"/>
@@ -56704,7 +56704,7 @@
       <c r="CK204" s="3"/>
       <c r="CN204" s="3"/>
     </row>
-    <row r="205" spans="3:95">
+    <row r="205" spans="3:95" x14ac:dyDescent="0.2">
       <c r="J205" s="5"/>
       <c r="K205" s="6"/>
       <c r="L205" s="6"/>
@@ -56719,7 +56719,7 @@
       <c r="CN205" s="3"/>
       <c r="CQ205" s="3"/>
     </row>
-    <row r="206" spans="3:95">
+    <row r="206" spans="3:95" x14ac:dyDescent="0.2">
       <c r="J206" s="5"/>
       <c r="K206" s="6"/>
       <c r="L206" s="6"/>
@@ -56732,7 +56732,7 @@
       <c r="CK206" s="3"/>
       <c r="CN206" s="3"/>
     </row>
-    <row r="207" spans="3:95">
+    <row r="207" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C207" s="1"/>
       <c r="D207" s="1"/>
       <c r="E207" s="1"/>
@@ -56752,7 +56752,7 @@
       <c r="CK207" s="3"/>
       <c r="CN207" s="3"/>
     </row>
-    <row r="208" spans="3:95">
+    <row r="208" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C208" s="1"/>
       <c r="D208" s="1"/>
       <c r="E208" s="1"/>
@@ -56773,7 +56773,7 @@
       <c r="CN208" s="3"/>
       <c r="CQ208" s="3"/>
     </row>
-    <row r="209" spans="3:95">
+    <row r="209" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C209" s="1"/>
       <c r="D209" s="1"/>
       <c r="E209" s="1"/>
@@ -56794,7 +56794,7 @@
       <c r="CN209" s="3"/>
       <c r="CQ209" s="3"/>
     </row>
-    <row r="210" spans="3:95">
+    <row r="210" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C210" s="1"/>
       <c r="D210" s="1"/>
       <c r="E210" s="1"/>
@@ -56814,7 +56814,7 @@
       <c r="CK210" s="3"/>
       <c r="CN210" s="3"/>
     </row>
-    <row r="211" spans="3:95">
+    <row r="211" spans="3:95" x14ac:dyDescent="0.2">
       <c r="J211" s="5"/>
       <c r="K211" s="6"/>
       <c r="L211" s="6"/>
@@ -56824,7 +56824,7 @@
       <c r="AX211" s="5"/>
       <c r="BB211" s="6"/>
     </row>
-    <row r="212" spans="3:95">
+    <row r="212" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C212" s="1"/>
       <c r="D212" s="1"/>
       <c r="E212" s="1"/>
@@ -56841,7 +56841,7 @@
       <c r="AX212" s="5"/>
       <c r="BB212" s="6"/>
     </row>
-    <row r="213" spans="3:95">
+    <row r="213" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C213" s="1"/>
       <c r="D213" s="1"/>
       <c r="E213" s="1"/>
@@ -56858,7 +56858,7 @@
       <c r="AX213" s="5"/>
       <c r="BB213" s="6"/>
     </row>
-    <row r="214" spans="3:95">
+    <row r="214" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C214" s="1"/>
       <c r="D214" s="1"/>
       <c r="E214" s="1"/>
@@ -56875,7 +56875,7 @@
       <c r="AX214" s="5"/>
       <c r="BB214" s="6"/>
     </row>
-    <row r="215" spans="3:95">
+    <row r="215" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C215" s="1"/>
       <c r="D215" s="1"/>
       <c r="E215" s="1"/>
@@ -56892,7 +56892,7 @@
       <c r="AX215" s="5"/>
       <c r="BB215" s="6"/>
     </row>
-    <row r="216" spans="3:95">
+    <row r="216" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C216" s="1"/>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
@@ -56909,7 +56909,7 @@
       <c r="AX216" s="5"/>
       <c r="BB216" s="6"/>
     </row>
-    <row r="217" spans="3:95">
+    <row r="217" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C217" s="1"/>
       <c r="D217" s="1"/>
       <c r="E217" s="1"/>
@@ -56927,7 +56927,7 @@
       <c r="AY217" s="3"/>
       <c r="BB217" s="6"/>
     </row>
-    <row r="218" spans="3:95">
+    <row r="218" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C218" s="1"/>
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
@@ -56944,7 +56944,7 @@
       <c r="AX218" s="5"/>
       <c r="BB218" s="6"/>
     </row>
-    <row r="219" spans="3:95">
+    <row r="219" spans="3:95" x14ac:dyDescent="0.2">
       <c r="J219" s="5"/>
       <c r="K219" s="6"/>
       <c r="L219" s="6"/>
@@ -56954,7 +56954,7 @@
       <c r="AX219" s="5"/>
       <c r="BB219" s="6"/>
     </row>
-    <row r="220" spans="3:95">
+    <row r="220" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C220" s="1"/>
       <c r="D220" s="1"/>
       <c r="E220" s="1"/>
@@ -56971,7 +56971,7 @@
       <c r="AX220" s="5"/>
       <c r="BB220" s="6"/>
     </row>
-    <row r="221" spans="3:95">
+    <row r="221" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C221" s="1"/>
       <c r="D221" s="1"/>
       <c r="E221" s="1"/>
@@ -56988,7 +56988,7 @@
       <c r="AX221" s="5"/>
       <c r="BB221" s="6"/>
     </row>
-    <row r="222" spans="3:95">
+    <row r="222" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C222" s="1"/>
       <c r="D222" s="1"/>
       <c r="E222" s="1"/>
@@ -57005,7 +57005,7 @@
       <c r="AX222" s="5"/>
       <c r="BB222" s="6"/>
     </row>
-    <row r="223" spans="3:95">
+    <row r="223" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C223" s="1"/>
       <c r="D223" s="1"/>
       <c r="E223" s="1"/>
@@ -57022,7 +57022,7 @@
       <c r="AX223" s="5"/>
       <c r="BB223" s="6"/>
     </row>
-    <row r="224" spans="3:95">
+    <row r="224" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C224" s="1"/>
       <c r="D224" s="1"/>
       <c r="E224" s="1"/>
@@ -57039,7 +57039,7 @@
       <c r="AX224" s="5"/>
       <c r="BB224" s="6"/>
     </row>
-    <row r="225" spans="3:54">
+    <row r="225" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C225" s="1"/>
       <c r="D225" s="1"/>
       <c r="E225" s="1"/>
@@ -57056,7 +57056,7 @@
       <c r="AX225" s="5"/>
       <c r="BB225" s="6"/>
     </row>
-    <row r="226" spans="3:54">
+    <row r="226" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C226" s="1"/>
       <c r="D226" s="1"/>
       <c r="E226" s="1"/>
@@ -57073,7 +57073,7 @@
       <c r="AX226" s="5"/>
       <c r="BB226" s="6"/>
     </row>
-    <row r="227" spans="3:54">
+    <row r="227" spans="3:54" x14ac:dyDescent="0.2">
       <c r="J227" s="5"/>
       <c r="K227" s="6"/>
       <c r="L227" s="6"/>
@@ -57083,7 +57083,7 @@
       <c r="AX227" s="5"/>
       <c r="BB227" s="6"/>
     </row>
-    <row r="228" spans="3:54">
+    <row r="228" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C228" s="1"/>
       <c r="D228" s="1"/>
       <c r="E228" s="1"/>
@@ -57101,7 +57101,7 @@
       <c r="AY228" s="3"/>
       <c r="BB228" s="6"/>
     </row>
-    <row r="229" spans="3:54">
+    <row r="229" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C229" s="1"/>
       <c r="D229" s="1"/>
       <c r="E229" s="1"/>
@@ -57118,7 +57118,7 @@
       <c r="AX229" s="5"/>
       <c r="BB229" s="6"/>
     </row>
-    <row r="230" spans="3:54">
+    <row r="230" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C230" s="1"/>
       <c r="D230" s="1"/>
       <c r="E230" s="1"/>
@@ -57135,7 +57135,7 @@
       <c r="AY230" s="3"/>
       <c r="BB230" s="6"/>
     </row>
-    <row r="231" spans="3:54">
+    <row r="231" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C231" s="1"/>
       <c r="D231" s="1"/>
       <c r="E231" s="1"/>
@@ -57152,7 +57152,7 @@
       <c r="AY231" s="3"/>
       <c r="BB231" s="6"/>
     </row>
-    <row r="232" spans="3:54">
+    <row r="232" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C232" s="1"/>
       <c r="D232" s="1"/>
       <c r="E232" s="1"/>
@@ -57168,7 +57168,7 @@
       <c r="AX232" s="5"/>
       <c r="BB232" s="6"/>
     </row>
-    <row r="233" spans="3:54">
+    <row r="233" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C233" s="1"/>
       <c r="D233" s="1"/>
       <c r="E233" s="1"/>
@@ -57185,7 +57185,7 @@
       <c r="AX233" s="5"/>
       <c r="BB233" s="6"/>
     </row>
-    <row r="234" spans="3:54">
+    <row r="234" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C234" s="1"/>
       <c r="D234" s="1"/>
       <c r="E234" s="1"/>
@@ -57202,7 +57202,7 @@
       <c r="AX234" s="5"/>
       <c r="BB234" s="6"/>
     </row>
-    <row r="235" spans="3:54">
+    <row r="235" spans="3:54" x14ac:dyDescent="0.2">
       <c r="J235" s="5"/>
       <c r="K235" s="6"/>
       <c r="L235" s="6"/>
@@ -57212,7 +57212,7 @@
       <c r="AX235" s="5"/>
       <c r="BB235" s="6"/>
     </row>
-    <row r="236" spans="3:54">
+    <row r="236" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C236" s="1"/>
       <c r="D236" s="1"/>
       <c r="E236" s="1"/>
@@ -57229,7 +57229,7 @@
       <c r="AX236" s="5"/>
       <c r="BB236" s="6"/>
     </row>
-    <row r="237" spans="3:54">
+    <row r="237" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C237" s="1"/>
       <c r="D237" s="1"/>
       <c r="E237" s="1"/>
@@ -57246,7 +57246,7 @@
       <c r="AX237" s="5"/>
       <c r="BB237" s="6"/>
     </row>
-    <row r="238" spans="3:54">
+    <row r="238" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C238" s="1"/>
       <c r="D238" s="1"/>
       <c r="E238" s="1"/>
@@ -57263,7 +57263,7 @@
       <c r="AX238" s="5"/>
       <c r="BB238" s="6"/>
     </row>
-    <row r="239" spans="3:54">
+    <row r="239" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C239" s="1"/>
       <c r="D239" s="1"/>
       <c r="E239" s="1"/>
@@ -57279,7 +57279,7 @@
       <c r="AX239" s="5"/>
       <c r="BB239" s="6"/>
     </row>
-    <row r="240" spans="3:54">
+    <row r="240" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C240" s="1"/>
       <c r="D240" s="1"/>
       <c r="E240" s="1"/>
@@ -57295,7 +57295,7 @@
       <c r="AX240" s="5"/>
       <c r="BB240" s="6"/>
     </row>
-    <row r="241" spans="3:54">
+    <row r="241" spans="3:54" x14ac:dyDescent="0.2">
       <c r="J241" s="5"/>
       <c r="K241" s="6"/>
       <c r="L241" s="6"/>
@@ -57306,7 +57306,7 @@
       <c r="AX241" s="5"/>
       <c r="BB241" s="6"/>
     </row>
-    <row r="242" spans="3:54">
+    <row r="242" spans="3:54" x14ac:dyDescent="0.2">
       <c r="J242" s="5"/>
       <c r="K242" s="6"/>
       <c r="L242" s="6"/>
@@ -57316,7 +57316,7 @@
       <c r="AX242" s="5"/>
       <c r="BB242" s="6"/>
     </row>
-    <row r="243" spans="3:54">
+    <row r="243" spans="3:54" x14ac:dyDescent="0.2">
       <c r="J243" s="5"/>
       <c r="K243" s="6"/>
       <c r="L243" s="6"/>
@@ -57326,7 +57326,7 @@
       <c r="AX243" s="5"/>
       <c r="BB243" s="6"/>
     </row>
-    <row r="244" spans="3:54">
+    <row r="244" spans="3:54" x14ac:dyDescent="0.2">
       <c r="J244" s="5"/>
       <c r="K244" s="6"/>
       <c r="L244" s="6"/>
@@ -57337,7 +57337,7 @@
       <c r="AX244" s="5"/>
       <c r="BB244" s="6"/>
     </row>
-    <row r="245" spans="3:54">
+    <row r="245" spans="3:54" x14ac:dyDescent="0.2">
       <c r="J245" s="5"/>
       <c r="K245" s="6"/>
       <c r="L245" s="6"/>
@@ -57349,7 +57349,7 @@
       <c r="AY245" s="3"/>
       <c r="BB245" s="6"/>
     </row>
-    <row r="246" spans="3:54">
+    <row r="246" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C246" s="1"/>
       <c r="D246" s="1"/>
       <c r="E246" s="1"/>
@@ -57366,7 +57366,7 @@
       <c r="AX246" s="5"/>
       <c r="BB246" s="6"/>
     </row>
-    <row r="247" spans="3:54">
+    <row r="247" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C247" s="1"/>
       <c r="D247" s="1"/>
       <c r="E247" s="1"/>
@@ -57382,7 +57382,7 @@
       <c r="AX247" s="5"/>
       <c r="BB247" s="6"/>
     </row>
-    <row r="248" spans="3:54">
+    <row r="248" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C248" s="1"/>
       <c r="D248" s="1"/>
       <c r="E248" s="1"/>
@@ -57400,7 +57400,7 @@
       <c r="AX248" s="5"/>
       <c r="BB248" s="6"/>
     </row>
-    <row r="249" spans="3:54">
+    <row r="249" spans="3:54" x14ac:dyDescent="0.2">
       <c r="J249" s="5"/>
       <c r="K249" s="6"/>
       <c r="L249" s="6"/>
@@ -57409,7 +57409,7 @@
       <c r="AR249" s="6"/>
       <c r="AX249" s="5"/>
     </row>
-    <row r="250" spans="3:54">
+    <row r="250" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C250" s="1"/>
       <c r="D250" s="1"/>
       <c r="E250" s="1"/>
@@ -57425,7 +57425,7 @@
       <c r="AS250" s="3"/>
       <c r="AX250" s="5"/>
     </row>
-    <row r="251" spans="3:54">
+    <row r="251" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C251" s="1"/>
       <c r="D251" s="1"/>
       <c r="E251" s="1"/>
@@ -57441,7 +57441,7 @@
       <c r="AS251" s="3"/>
       <c r="AX251" s="5"/>
     </row>
-    <row r="252" spans="3:54">
+    <row r="252" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C252" s="1"/>
       <c r="D252" s="1"/>
       <c r="E252" s="1"/>
@@ -57457,7 +57457,7 @@
       <c r="AS252" s="3"/>
       <c r="AX252" s="5"/>
     </row>
-    <row r="253" spans="3:54">
+    <row r="253" spans="3:54" x14ac:dyDescent="0.2">
       <c r="J253" s="5"/>
       <c r="K253" s="6"/>
       <c r="L253" s="6"/>
@@ -57466,7 +57466,7 @@
       <c r="AR253" s="6"/>
       <c r="AX253" s="5"/>
     </row>
-    <row r="254" spans="3:54">
+    <row r="254" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C254" s="1"/>
       <c r="D254" s="1"/>
       <c r="E254" s="1"/>
@@ -57482,7 +57482,7 @@
       <c r="AS254" s="3"/>
       <c r="AX254" s="5"/>
     </row>
-    <row r="255" spans="3:54">
+    <row r="255" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C255" s="1"/>
       <c r="D255" s="1"/>
       <c r="E255" s="1"/>
@@ -57499,7 +57499,7 @@
       <c r="AX255" s="5"/>
       <c r="AY255" s="3"/>
     </row>
-    <row r="256" spans="3:54">
+    <row r="256" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C256" s="1"/>
       <c r="D256" s="1"/>
       <c r="E256" s="1"/>
@@ -57515,7 +57515,7 @@
       <c r="AS256" s="3"/>
       <c r="AX256" s="5"/>
     </row>
-    <row r="257" spans="3:57">
+    <row r="257" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C257" s="1"/>
       <c r="D257" s="1"/>
       <c r="E257" s="1"/>
@@ -57531,7 +57531,7 @@
       <c r="AS257" s="3"/>
       <c r="AX257" s="5"/>
     </row>
-    <row r="258" spans="3:57">
+    <row r="258" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C258" s="1"/>
       <c r="D258" s="1"/>
       <c r="E258" s="1"/>
@@ -57546,7 +57546,7 @@
       <c r="AR258" s="6"/>
       <c r="AX258" s="5"/>
     </row>
-    <row r="259" spans="3:57">
+    <row r="259" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C259" s="1"/>
       <c r="D259" s="1"/>
       <c r="E259" s="1"/>
@@ -57562,7 +57562,7 @@
       <c r="AS259" s="3"/>
       <c r="AX259" s="5"/>
     </row>
-    <row r="260" spans="3:57">
+    <row r="260" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C260" s="1"/>
       <c r="D260" s="1"/>
       <c r="E260" s="1"/>
@@ -57576,14 +57576,14 @@
       <c r="AS260" s="3"/>
       <c r="AX260" s="5"/>
     </row>
-    <row r="261" spans="3:57">
+    <row r="261" spans="3:57" x14ac:dyDescent="0.2">
       <c r="J261" s="5"/>
       <c r="AM261" s="6"/>
       <c r="AQ261" s="6"/>
       <c r="AR261" s="6"/>
       <c r="AX261" s="5"/>
     </row>
-    <row r="262" spans="3:57">
+    <row r="262" spans="3:57" x14ac:dyDescent="0.2">
       <c r="J262" s="5"/>
       <c r="AM262" s="6"/>
       <c r="AQ262" s="6"/>
@@ -57592,7 +57592,7 @@
       <c r="AX262" s="5"/>
       <c r="BE262" s="3"/>
     </row>
-    <row r="263" spans="3:57">
+    <row r="263" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C263" s="1"/>
       <c r="D263" s="1"/>
       <c r="E263" s="1"/>
@@ -57607,7 +57607,7 @@
       <c r="AX263" s="5"/>
       <c r="BE263" s="3"/>
     </row>
-    <row r="264" spans="3:57">
+    <row r="264" spans="3:57" x14ac:dyDescent="0.2">
       <c r="J264" s="5"/>
       <c r="AM264" s="6"/>
       <c r="AQ264" s="6"/>
@@ -57615,14 +57615,14 @@
       <c r="AS264" s="3"/>
       <c r="AX264" s="5"/>
     </row>
-    <row r="265" spans="3:57">
+    <row r="265" spans="3:57" x14ac:dyDescent="0.2">
       <c r="J265" s="5"/>
       <c r="AM265" s="6"/>
       <c r="AQ265" s="6"/>
       <c r="AR265" s="6"/>
       <c r="AX265" s="5"/>
     </row>
-    <row r="266" spans="3:57">
+    <row r="266" spans="3:57" x14ac:dyDescent="0.2">
       <c r="J266" s="5"/>
       <c r="AM266" s="6"/>
       <c r="AQ266" s="6"/>
@@ -57630,14 +57630,14 @@
       <c r="AS266" s="3"/>
       <c r="AX266" s="5"/>
     </row>
-    <row r="267" spans="3:57">
+    <row r="267" spans="3:57" x14ac:dyDescent="0.2">
       <c r="J267" s="5"/>
       <c r="AM267" s="6"/>
       <c r="AQ267" s="6"/>
       <c r="AR267" s="6"/>
       <c r="AX267" s="5"/>
     </row>
-    <row r="268" spans="3:57">
+    <row r="268" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C268" s="1"/>
       <c r="D268" s="1"/>
       <c r="E268" s="1"/>
@@ -57651,7 +57651,7 @@
       <c r="AS268" s="3"/>
       <c r="AX268" s="5"/>
     </row>
-    <row r="269" spans="3:57">
+    <row r="269" spans="3:57" x14ac:dyDescent="0.2">
       <c r="J269" s="5"/>
       <c r="AM269" s="6"/>
       <c r="AQ269" s="6"/>
@@ -57660,7 +57660,7 @@
       <c r="AX269" s="5"/>
       <c r="AY269" s="3"/>
     </row>
-    <row r="270" spans="3:57">
+    <row r="270" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C270" s="1"/>
       <c r="D270" s="1"/>
       <c r="E270" s="1"/>
@@ -57675,7 +57675,7 @@
       <c r="AX270" s="5"/>
       <c r="BE270" s="3"/>
     </row>
-    <row r="271" spans="3:57">
+    <row r="271" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C271" s="1"/>
       <c r="D271" s="1"/>
       <c r="E271" s="1"/>
@@ -57688,14 +57688,14 @@
       <c r="AR271" s="6"/>
       <c r="AX271" s="5"/>
     </row>
-    <row r="272" spans="3:57">
+    <row r="272" spans="3:57" x14ac:dyDescent="0.2">
       <c r="J272" s="5"/>
       <c r="AM272" s="6"/>
       <c r="AQ272" s="6"/>
       <c r="AR272" s="6"/>
       <c r="AX272" s="5"/>
     </row>
-    <row r="273" spans="3:95">
+    <row r="273" spans="3:95" x14ac:dyDescent="0.2">
       <c r="J273" s="5"/>
       <c r="AM273" s="6"/>
       <c r="AQ273" s="6"/>
@@ -57703,7 +57703,7 @@
       <c r="AS273" s="3"/>
       <c r="AX273" s="5"/>
     </row>
-    <row r="274" spans="3:95">
+    <row r="274" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C274" s="1"/>
       <c r="D274" s="1"/>
       <c r="E274" s="1"/>
@@ -57716,7 +57716,7 @@
       <c r="AR274" s="6"/>
       <c r="AX274" s="5"/>
     </row>
-    <row r="275" spans="3:95">
+    <row r="275" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C275" s="1"/>
       <c r="D275" s="1"/>
       <c r="E275" s="1"/>
@@ -57729,7 +57729,7 @@
       <c r="AR275" s="6"/>
       <c r="AX275" s="5"/>
     </row>
-    <row r="276" spans="3:95">
+    <row r="276" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C276" s="1"/>
       <c r="D276" s="1"/>
       <c r="E276" s="1"/>
@@ -57742,7 +57742,7 @@
       <c r="AR276" s="6"/>
       <c r="AX276" s="5"/>
     </row>
-    <row r="277" spans="3:95">
+    <row r="277" spans="3:95" x14ac:dyDescent="0.2">
       <c r="J277" s="5"/>
       <c r="AM277" s="6"/>
       <c r="AQ277" s="6"/>
@@ -57751,7 +57751,7 @@
       <c r="AX277" s="5"/>
       <c r="AY277" s="3"/>
     </row>
-    <row r="278" spans="3:95">
+    <row r="278" spans="3:95" x14ac:dyDescent="0.2">
       <c r="J278" s="5"/>
       <c r="AM278" s="6"/>
       <c r="AQ278" s="6"/>
@@ -57760,14 +57760,14 @@
       <c r="AX278" s="5"/>
       <c r="AY278" s="3"/>
     </row>
-    <row r="279" spans="3:95">
+    <row r="279" spans="3:95" x14ac:dyDescent="0.2">
       <c r="J279" s="5"/>
       <c r="AM279" s="6"/>
       <c r="AQ279" s="6"/>
       <c r="AR279" s="6"/>
       <c r="AX279" s="5"/>
     </row>
-    <row r="280" spans="3:95">
+    <row r="280" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C280" s="1"/>
       <c r="D280" s="1"/>
       <c r="E280" s="1"/>
@@ -57785,7 +57785,7 @@
       <c r="CN280" s="3"/>
       <c r="CQ280" s="3"/>
     </row>
-    <row r="281" spans="3:95">
+    <row r="281" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C281" s="1"/>
       <c r="D281" s="1"/>
       <c r="E281" s="1"/>
@@ -57799,7 +57799,7 @@
       <c r="AS281" s="3"/>
       <c r="AX281" s="5"/>
     </row>
-    <row r="282" spans="3:95">
+    <row r="282" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C282" s="1"/>
       <c r="D282" s="1"/>
       <c r="E282" s="1"/>
@@ -57813,7 +57813,7 @@
       <c r="AS282" s="3"/>
       <c r="AX282" s="5"/>
     </row>
-    <row r="283" spans="3:95">
+    <row r="283" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C283" s="1"/>
       <c r="D283" s="1"/>
       <c r="E283" s="1"/>
@@ -57826,7 +57826,7 @@
       <c r="AR283" s="6"/>
       <c r="AX283" s="5"/>
     </row>
-    <row r="284" spans="3:95">
+    <row r="284" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C284" s="1"/>
       <c r="D284" s="1"/>
       <c r="E284" s="1"/>
@@ -57840,7 +57840,7 @@
       <c r="AS284" s="3"/>
       <c r="AX284" s="5"/>
     </row>
-    <row r="285" spans="3:95">
+    <row r="285" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C285" s="1"/>
       <c r="D285" s="1"/>
       <c r="E285" s="1"/>
@@ -57854,7 +57854,7 @@
       <c r="AS285" s="3"/>
       <c r="AX285" s="5"/>
     </row>
-    <row r="286" spans="3:95">
+    <row r="286" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C286" s="1"/>
       <c r="D286" s="1"/>
       <c r="E286" s="1"/>
@@ -57868,14 +57868,14 @@
       <c r="AS286" s="3"/>
       <c r="AX286" s="5"/>
     </row>
-    <row r="287" spans="3:95">
+    <row r="287" spans="3:95" x14ac:dyDescent="0.2">
       <c r="J287" s="5"/>
       <c r="AM287" s="6"/>
       <c r="AQ287" s="6"/>
       <c r="AR287" s="6"/>
       <c r="AX287" s="5"/>
     </row>
-    <row r="288" spans="3:95">
+    <row r="288" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C288" s="1"/>
       <c r="D288" s="1"/>
       <c r="E288" s="1"/>
@@ -57888,7 +57888,7 @@
       <c r="AR288" s="6"/>
       <c r="AX288" s="5"/>
     </row>
-    <row r="289" spans="3:50">
+    <row r="289" spans="3:50" x14ac:dyDescent="0.2">
       <c r="J289" s="5"/>
       <c r="AM289" s="6"/>
       <c r="AQ289" s="6"/>
@@ -57896,7 +57896,7 @@
       <c r="AS289" s="3"/>
       <c r="AX289" s="5"/>
     </row>
-    <row r="290" spans="3:50">
+    <row r="290" spans="3:50" x14ac:dyDescent="0.2">
       <c r="J290" s="5"/>
       <c r="AM290" s="6"/>
       <c r="AQ290" s="6"/>
@@ -57904,7 +57904,7 @@
       <c r="AS290" s="3"/>
       <c r="AX290" s="5"/>
     </row>
-    <row r="291" spans="3:50">
+    <row r="291" spans="3:50" x14ac:dyDescent="0.2">
       <c r="J291" s="5"/>
       <c r="AM291" s="6"/>
       <c r="AQ291" s="6"/>
@@ -57912,7 +57912,7 @@
       <c r="AS291" s="3"/>
       <c r="AX291" s="5"/>
     </row>
-    <row r="292" spans="3:50">
+    <row r="292" spans="3:50" x14ac:dyDescent="0.2">
       <c r="C292" s="1"/>
       <c r="D292" s="1"/>
       <c r="E292" s="1"/>
@@ -57925,14 +57925,14 @@
       <c r="AR292" s="6"/>
       <c r="AX292" s="5"/>
     </row>
-    <row r="293" spans="3:50">
+    <row r="293" spans="3:50" x14ac:dyDescent="0.2">
       <c r="J293" s="5"/>
       <c r="AM293" s="6"/>
       <c r="AQ293" s="6"/>
       <c r="AR293" s="6"/>
       <c r="AX293" s="5"/>
     </row>
-    <row r="294" spans="3:50">
+    <row r="294" spans="3:50" x14ac:dyDescent="0.2">
       <c r="C294" s="1"/>
       <c r="D294" s="1"/>
       <c r="E294" s="1"/>
@@ -57946,14 +57946,14 @@
       <c r="AS294" s="3"/>
       <c r="AX294" s="5"/>
     </row>
-    <row r="295" spans="3:50">
+    <row r="295" spans="3:50" x14ac:dyDescent="0.2">
       <c r="J295" s="5"/>
       <c r="AM295" s="6"/>
       <c r="AQ295" s="6"/>
       <c r="AR295" s="6"/>
       <c r="AX295" s="5"/>
     </row>
-    <row r="296" spans="3:50">
+    <row r="296" spans="3:50" x14ac:dyDescent="0.2">
       <c r="C296" s="1"/>
       <c r="D296" s="1"/>
       <c r="E296" s="1"/>
@@ -57966,7 +57966,7 @@
       <c r="AR296" s="6"/>
       <c r="AX296" s="5"/>
     </row>
-    <row r="297" spans="3:50">
+    <row r="297" spans="3:50" x14ac:dyDescent="0.2">
       <c r="C297" s="1"/>
       <c r="D297" s="1"/>
       <c r="E297" s="1"/>
@@ -57979,7 +57979,7 @@
       <c r="AR297" s="6"/>
       <c r="AX297" s="5"/>
     </row>
-    <row r="298" spans="3:50">
+    <row r="298" spans="3:50" x14ac:dyDescent="0.2">
       <c r="C298" s="1"/>
       <c r="D298" s="1"/>
       <c r="E298" s="1"/>
@@ -57992,21 +57992,21 @@
       <c r="AR298" s="6"/>
       <c r="AX298" s="5"/>
     </row>
-    <row r="299" spans="3:50">
+    <row r="299" spans="3:50" x14ac:dyDescent="0.2">
       <c r="J299" s="5"/>
       <c r="AM299" s="6"/>
       <c r="AQ299" s="6"/>
       <c r="AR299" s="6"/>
       <c r="AX299" s="5"/>
     </row>
-    <row r="300" spans="3:50">
+    <row r="300" spans="3:50" x14ac:dyDescent="0.2">
       <c r="J300" s="5"/>
       <c r="AM300" s="6"/>
       <c r="AQ300" s="6"/>
       <c r="AR300" s="6"/>
       <c r="AX300" s="5"/>
     </row>
-    <row r="301" spans="3:50">
+    <row r="301" spans="3:50" x14ac:dyDescent="0.2">
       <c r="C301" s="1"/>
       <c r="D301" s="1"/>
       <c r="E301" s="1"/>
@@ -58019,7 +58019,7 @@
       <c r="AR301" s="6"/>
       <c r="AX301" s="5"/>
     </row>
-    <row r="302" spans="3:50">
+    <row r="302" spans="3:50" x14ac:dyDescent="0.2">
       <c r="C302" s="1"/>
       <c r="D302" s="1"/>
       <c r="E302" s="1"/>
@@ -58033,7 +58033,7 @@
       <c r="AS302" s="3"/>
       <c r="AX302" s="5"/>
     </row>
-    <row r="303" spans="3:50">
+    <row r="303" spans="3:50" x14ac:dyDescent="0.2">
       <c r="C303" s="1"/>
       <c r="D303" s="1"/>
       <c r="E303" s="1"/>
@@ -58046,7 +58046,7 @@
       <c r="AR303" s="6"/>
       <c r="AX303" s="5"/>
     </row>
-    <row r="304" spans="3:50">
+    <row r="304" spans="3:50" x14ac:dyDescent="0.2">
       <c r="C304" s="1"/>
       <c r="D304" s="1"/>
       <c r="E304" s="1"/>
@@ -58059,7 +58059,7 @@
       <c r="AR304" s="6"/>
       <c r="AX304" s="5"/>
     </row>
-    <row r="305" spans="3:51">
+    <row r="305" spans="3:51" x14ac:dyDescent="0.2">
       <c r="J305" s="5"/>
       <c r="AM305" s="6"/>
       <c r="AQ305" s="6"/>
@@ -58067,7 +58067,7 @@
       <c r="AS305" s="3"/>
       <c r="AX305" s="5"/>
     </row>
-    <row r="306" spans="3:51">
+    <row r="306" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C306" s="1"/>
       <c r="D306" s="1"/>
       <c r="E306" s="1"/>
@@ -58081,14 +58081,14 @@
       <c r="AR306" s="6"/>
       <c r="AX306" s="5"/>
     </row>
-    <row r="307" spans="3:51">
+    <row r="307" spans="3:51" x14ac:dyDescent="0.2">
       <c r="J307" s="5"/>
       <c r="AM307" s="6"/>
       <c r="AQ307" s="6"/>
       <c r="AR307" s="6"/>
       <c r="AX307" s="5"/>
     </row>
-    <row r="308" spans="3:51">
+    <row r="308" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C308" s="1"/>
       <c r="D308" s="1"/>
       <c r="E308" s="1"/>
@@ -58102,7 +58102,7 @@
       <c r="AS308" s="3"/>
       <c r="AX308" s="5"/>
     </row>
-    <row r="309" spans="3:51">
+    <row r="309" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C309" s="1"/>
       <c r="D309" s="1"/>
       <c r="E309" s="1"/>
@@ -58117,7 +58117,7 @@
       <c r="AX309" s="5"/>
       <c r="AY309" s="3"/>
     </row>
-    <row r="310" spans="3:51">
+    <row r="310" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C310" s="1"/>
       <c r="D310" s="1"/>
       <c r="E310" s="1"/>
@@ -58131,7 +58131,7 @@
       <c r="AS310" s="3"/>
       <c r="AX310" s="5"/>
     </row>
-    <row r="311" spans="3:51">
+    <row r="311" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C311" s="1"/>
       <c r="D311" s="1"/>
       <c r="E311" s="1"/>
@@ -58145,7 +58145,7 @@
       <c r="AS311" s="3"/>
       <c r="AX311" s="5"/>
     </row>
-    <row r="312" spans="3:51">
+    <row r="312" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C312" s="1"/>
       <c r="D312" s="1"/>
       <c r="E312" s="1"/>
@@ -58159,7 +58159,7 @@
       <c r="AS312" s="3"/>
       <c r="AX312" s="5"/>
     </row>
-    <row r="313" spans="3:51">
+    <row r="313" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C313" s="1"/>
       <c r="D313" s="1"/>
       <c r="E313" s="1"/>
@@ -58173,7 +58173,7 @@
       <c r="AS313" s="3"/>
       <c r="AX313" s="5"/>
     </row>
-    <row r="314" spans="3:51">
+    <row r="314" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C314" s="1"/>
       <c r="D314" s="1"/>
       <c r="E314" s="1"/>
@@ -58187,14 +58187,14 @@
       <c r="AS314" s="3"/>
       <c r="AX314" s="5"/>
     </row>
-    <row r="315" spans="3:51">
+    <row r="315" spans="3:51" x14ac:dyDescent="0.2">
       <c r="J315" s="5"/>
       <c r="AM315" s="6"/>
       <c r="AQ315" s="6"/>
       <c r="AR315" s="6"/>
       <c r="AX315" s="5"/>
     </row>
-    <row r="316" spans="3:51">
+    <row r="316" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C316" s="1"/>
       <c r="D316" s="1"/>
       <c r="E316" s="1"/>
@@ -58207,14 +58207,14 @@
       <c r="AR316" s="6"/>
       <c r="AX316" s="5"/>
     </row>
-    <row r="317" spans="3:51">
+    <row r="317" spans="3:51" x14ac:dyDescent="0.2">
       <c r="J317" s="5"/>
       <c r="AM317" s="6"/>
       <c r="AQ317" s="6"/>
       <c r="AR317" s="6"/>
       <c r="AX317" s="5"/>
     </row>
-    <row r="318" spans="3:51">
+    <row r="318" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C318" s="1"/>
       <c r="D318" s="1"/>
       <c r="E318" s="1"/>
@@ -58227,7 +58227,7 @@
       <c r="AR318" s="6"/>
       <c r="AX318" s="5"/>
     </row>
-    <row r="319" spans="3:51">
+    <row r="319" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C319" s="1"/>
       <c r="D319" s="1"/>
       <c r="E319" s="1"/>
@@ -58240,7 +58240,7 @@
       <c r="AR319" s="6"/>
       <c r="AX319" s="5"/>
     </row>
-    <row r="320" spans="3:51">
+    <row r="320" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C320" s="1"/>
       <c r="D320" s="1"/>
       <c r="E320" s="1"/>
@@ -58253,7 +58253,7 @@
       <c r="AR320" s="6"/>
       <c r="AX320" s="5"/>
     </row>
-    <row r="321" spans="3:57">
+    <row r="321" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C321" s="1"/>
       <c r="D321" s="1"/>
       <c r="E321" s="1"/>
@@ -58266,7 +58266,7 @@
       <c r="AR321" s="6"/>
       <c r="AX321" s="5"/>
     </row>
-    <row r="322" spans="3:57">
+    <row r="322" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C322" s="1"/>
       <c r="D322" s="1"/>
       <c r="E322" s="1"/>
@@ -58279,7 +58279,7 @@
       <c r="AR322" s="6"/>
       <c r="AX322" s="5"/>
     </row>
-    <row r="323" spans="3:57">
+    <row r="323" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C323" s="1"/>
       <c r="D323" s="1"/>
       <c r="E323" s="1"/>
@@ -58292,12 +58292,12 @@
       <c r="AR323" s="3"/>
       <c r="AX323" s="5"/>
     </row>
-    <row r="324" spans="3:57">
+    <row r="324" spans="3:57" x14ac:dyDescent="0.2">
       <c r="J324" s="5"/>
       <c r="AM324" s="6"/>
       <c r="AX324" s="5"/>
     </row>
-    <row r="325" spans="3:57">
+    <row r="325" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C325" s="1"/>
       <c r="D325" s="1"/>
       <c r="E325" s="1"/>
@@ -58308,7 +58308,7 @@
       <c r="AM325" s="6"/>
       <c r="AX325" s="5"/>
     </row>
-    <row r="326" spans="3:57">
+    <row r="326" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C326" s="1"/>
       <c r="D326" s="1"/>
       <c r="E326" s="1"/>
@@ -58319,7 +58319,7 @@
       <c r="AM326" s="6"/>
       <c r="AX326" s="5"/>
     </row>
-    <row r="327" spans="3:57">
+    <row r="327" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C327" s="1"/>
       <c r="D327" s="1"/>
       <c r="E327" s="1"/>
@@ -58331,7 +58331,7 @@
       <c r="AM327" s="6"/>
       <c r="AX327" s="5"/>
     </row>
-    <row r="328" spans="3:57">
+    <row r="328" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C328" s="1"/>
       <c r="D328" s="1"/>
       <c r="E328" s="1"/>
@@ -58342,7 +58342,7 @@
       <c r="AM328" s="6"/>
       <c r="AX328" s="5"/>
     </row>
-    <row r="329" spans="3:57">
+    <row r="329" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C329" s="1"/>
       <c r="D329" s="1"/>
       <c r="E329" s="1"/>
@@ -58358,12 +58358,12 @@
       <c r="AX329" s="5"/>
       <c r="BE329" s="3"/>
     </row>
-    <row r="330" spans="3:57">
+    <row r="330" spans="3:57" x14ac:dyDescent="0.2">
       <c r="J330" s="5"/>
       <c r="AM330" s="6"/>
       <c r="AX330" s="5"/>
     </row>
-    <row r="331" spans="3:57">
+    <row r="331" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C331" s="1"/>
       <c r="D331" s="1"/>
       <c r="E331" s="1"/>
@@ -58374,12 +58374,12 @@
       <c r="AM331" s="6"/>
       <c r="AX331" s="5"/>
     </row>
-    <row r="332" spans="3:57">
+    <row r="332" spans="3:57" x14ac:dyDescent="0.2">
       <c r="J332" s="5"/>
       <c r="AM332" s="6"/>
       <c r="AX332" s="5"/>
     </row>
-    <row r="333" spans="3:57">
+    <row r="333" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C333" s="1"/>
       <c r="D333" s="1"/>
       <c r="E333" s="1"/>
@@ -58392,7 +58392,7 @@
       <c r="AR333" s="3"/>
       <c r="AX333" s="5"/>
     </row>
-    <row r="334" spans="3:57">
+    <row r="334" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C334" s="1"/>
       <c r="D334" s="1"/>
       <c r="E334" s="1"/>
@@ -58406,7 +58406,7 @@
       <c r="AX334" s="5"/>
       <c r="AY334" s="3"/>
     </row>
-    <row r="335" spans="3:57">
+    <row r="335" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C335" s="1"/>
       <c r="D335" s="1"/>
       <c r="E335" s="1"/>
@@ -58419,7 +58419,7 @@
       <c r="AR335" s="3"/>
       <c r="AX335" s="5"/>
     </row>
-    <row r="336" spans="3:57">
+    <row r="336" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C336" s="1"/>
       <c r="D336" s="1"/>
       <c r="E336" s="1"/>
@@ -58432,7 +58432,7 @@
       <c r="AR336" s="3"/>
       <c r="AX336" s="5"/>
     </row>
-    <row r="337" spans="3:51">
+    <row r="337" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C337" s="1"/>
       <c r="D337" s="1"/>
       <c r="E337" s="1"/>
@@ -58446,7 +58446,7 @@
       <c r="AX337" s="5"/>
       <c r="AY337" s="3"/>
     </row>
-    <row r="338" spans="3:51">
+    <row r="338" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C338" s="1"/>
       <c r="D338" s="1"/>
       <c r="E338" s="1"/>
@@ -58460,7 +58460,7 @@
       <c r="AX338" s="5"/>
       <c r="AY338" s="3"/>
     </row>
-    <row r="339" spans="3:51">
+    <row r="339" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C339" s="1"/>
       <c r="D339" s="1"/>
       <c r="E339" s="1"/>
@@ -58471,24 +58471,24 @@
       <c r="AM339" s="6"/>
       <c r="AX339" s="5"/>
     </row>
-    <row r="340" spans="3:51">
+    <row r="340" spans="3:51" x14ac:dyDescent="0.2">
       <c r="J340" s="5"/>
       <c r="AM340" s="6"/>
       <c r="AX340" s="5"/>
     </row>
-    <row r="341" spans="3:51">
+    <row r="341" spans="3:51" x14ac:dyDescent="0.2">
       <c r="J341" s="5"/>
       <c r="AM341" s="6"/>
       <c r="AQ341" s="3"/>
       <c r="AR341" s="3"/>
       <c r="AX341" s="5"/>
     </row>
-    <row r="342" spans="3:51">
+    <row r="342" spans="3:51" x14ac:dyDescent="0.2">
       <c r="J342" s="5"/>
       <c r="AM342" s="6"/>
       <c r="AX342" s="5"/>
     </row>
-    <row r="343" spans="3:51">
+    <row r="343" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C343" s="1"/>
       <c r="D343" s="1"/>
       <c r="E343" s="1"/>
@@ -58501,7 +58501,7 @@
       <c r="AR343" s="3"/>
       <c r="AX343" s="5"/>
     </row>
-    <row r="344" spans="3:51">
+    <row r="344" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C344" s="1"/>
       <c r="D344" s="1"/>
       <c r="E344" s="1"/>
@@ -58514,7 +58514,7 @@
       <c r="AR344" s="3"/>
       <c r="AX344" s="5"/>
     </row>
-    <row r="345" spans="3:51">
+    <row r="345" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C345" s="1"/>
       <c r="D345" s="1"/>
       <c r="E345" s="1"/>
@@ -58527,7 +58527,7 @@
       <c r="AR345" s="3"/>
       <c r="AX345" s="5"/>
     </row>
-    <row r="346" spans="3:51">
+    <row r="346" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C346" s="1"/>
       <c r="D346" s="1"/>
       <c r="E346" s="1"/>
@@ -58540,7 +58540,7 @@
       <c r="AR346" s="3"/>
       <c r="AX346" s="5"/>
     </row>
-    <row r="347" spans="3:51">
+    <row r="347" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C347" s="1"/>
       <c r="D347" s="1"/>
       <c r="E347" s="1"/>
@@ -58551,7 +58551,7 @@
       <c r="AM347" s="6"/>
       <c r="AX347" s="5"/>
     </row>
-    <row r="348" spans="3:51">
+    <row r="348" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C348" s="1"/>
       <c r="D348" s="1"/>
       <c r="E348" s="1"/>
@@ -58562,7 +58562,7 @@
       <c r="AM348" s="6"/>
       <c r="AX348" s="5"/>
     </row>
-    <row r="349" spans="3:51">
+    <row r="349" spans="3:51" x14ac:dyDescent="0.2">
       <c r="J349" s="5"/>
       <c r="AM349" s="6"/>
       <c r="AQ349" s="3"/>
@@ -58570,12 +58570,12 @@
       <c r="AX349" s="5"/>
       <c r="AY349" s="3"/>
     </row>
-    <row r="350" spans="3:51">
+    <row r="350" spans="3:51" x14ac:dyDescent="0.2">
       <c r="J350" s="5"/>
       <c r="AM350" s="6"/>
       <c r="AX350" s="5"/>
     </row>
-    <row r="351" spans="3:51">
+    <row r="351" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C351" s="1"/>
       <c r="D351" s="1"/>
       <c r="E351" s="1"/>
@@ -58588,7 +58588,7 @@
       <c r="AR351" s="3"/>
       <c r="AX351" s="5"/>
     </row>
-    <row r="352" spans="3:51">
+    <row r="352" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C352" s="1"/>
       <c r="D352" s="1"/>
       <c r="E352" s="1"/>
@@ -58601,7 +58601,7 @@
       <c r="AR352" s="3"/>
       <c r="AX352" s="5"/>
     </row>
-    <row r="353" spans="3:86">
+    <row r="353" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C353" s="1"/>
       <c r="D353" s="1"/>
       <c r="E353" s="1"/>
@@ -58612,7 +58612,7 @@
       <c r="AM353" s="6"/>
       <c r="AX353" s="5"/>
     </row>
-    <row r="354" spans="3:86">
+    <row r="354" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C354" s="1"/>
       <c r="D354" s="1"/>
       <c r="E354" s="1"/>
@@ -58625,7 +58625,7 @@
       <c r="AR354" s="3"/>
       <c r="AX354" s="5"/>
     </row>
-    <row r="355" spans="3:86">
+    <row r="355" spans="3:86" x14ac:dyDescent="0.2">
       <c r="J355" s="5"/>
       <c r="AM355" s="6"/>
       <c r="AQ355" s="3"/>
@@ -58633,7 +58633,7 @@
       <c r="AX355" s="5"/>
       <c r="AY355" s="3"/>
     </row>
-    <row r="356" spans="3:86">
+    <row r="356" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C356" s="1"/>
       <c r="D356" s="1"/>
       <c r="E356" s="1"/>
@@ -58646,7 +58646,7 @@
       <c r="AR356" s="3"/>
       <c r="AX356" s="5"/>
     </row>
-    <row r="357" spans="3:86">
+    <row r="357" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C357" s="1"/>
       <c r="D357" s="1"/>
       <c r="E357" s="1"/>
@@ -58657,12 +58657,12 @@
       <c r="AM357" s="6"/>
       <c r="AX357" s="5"/>
     </row>
-    <row r="358" spans="3:86">
+    <row r="358" spans="3:86" x14ac:dyDescent="0.2">
       <c r="J358" s="5"/>
       <c r="AM358" s="6"/>
       <c r="AX358" s="5"/>
     </row>
-    <row r="359" spans="3:86">
+    <row r="359" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C359" s="1"/>
       <c r="D359" s="1"/>
       <c r="E359" s="1"/>
@@ -58673,7 +58673,7 @@
       <c r="AM359" s="6"/>
       <c r="AX359" s="5"/>
     </row>
-    <row r="360" spans="3:86">
+    <row r="360" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C360" s="1"/>
       <c r="D360" s="1"/>
       <c r="E360" s="1"/>
@@ -58684,17 +58684,17 @@
       <c r="AM360" s="6"/>
       <c r="AX360" s="5"/>
     </row>
-    <row r="361" spans="3:86">
+    <row r="361" spans="3:86" x14ac:dyDescent="0.2">
       <c r="J361" s="5"/>
       <c r="AM361" s="6"/>
       <c r="AX361" s="5"/>
     </row>
-    <row r="362" spans="3:86">
+    <row r="362" spans="3:86" x14ac:dyDescent="0.2">
       <c r="J362" s="5"/>
       <c r="AM362" s="6"/>
       <c r="AX362" s="5"/>
     </row>
-    <row r="363" spans="3:86">
+    <row r="363" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C363" s="1"/>
       <c r="D363" s="1"/>
       <c r="E363" s="1"/>
@@ -58705,19 +58705,19 @@
       <c r="AM363" s="6"/>
       <c r="AX363" s="5"/>
     </row>
-    <row r="364" spans="3:86">
+    <row r="364" spans="3:86" x14ac:dyDescent="0.2">
       <c r="J364" s="5"/>
       <c r="AM364" s="6"/>
       <c r="AQ364" s="3"/>
       <c r="AR364" s="3"/>
       <c r="AX364" s="5"/>
     </row>
-    <row r="365" spans="3:86">
+    <row r="365" spans="3:86" x14ac:dyDescent="0.2">
       <c r="J365" s="5"/>
       <c r="AM365" s="6"/>
       <c r="AX365" s="5"/>
     </row>
-    <row r="366" spans="3:86">
+    <row r="366" spans="3:86" x14ac:dyDescent="0.2">
       <c r="J366" s="5"/>
       <c r="AM366" s="6"/>
       <c r="AQ366" s="3"/>
@@ -58726,7 +58726,7 @@
       <c r="AX366" s="5"/>
       <c r="CH366" s="3"/>
     </row>
-    <row r="367" spans="3:86">
+    <row r="367" spans="3:86" x14ac:dyDescent="0.2">
       <c r="J367" s="5"/>
       <c r="AM367" s="6"/>
       <c r="AQ367" s="3"/>
@@ -58734,7 +58734,7 @@
       <c r="AS367" s="3"/>
       <c r="AX367" s="5"/>
     </row>
-    <row r="368" spans="3:86">
+    <row r="368" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C368" s="1"/>
       <c r="D368" s="1"/>
       <c r="E368" s="1"/>
@@ -58748,7 +58748,7 @@
       <c r="AS368" s="3"/>
       <c r="AX368" s="5"/>
     </row>
-    <row r="369" spans="3:92">
+    <row r="369" spans="3:92" x14ac:dyDescent="0.2">
       <c r="J369" s="5"/>
       <c r="AM369" s="6"/>
       <c r="AQ369" s="3"/>
@@ -58756,7 +58756,7 @@
       <c r="AS369" s="3"/>
       <c r="AX369" s="5"/>
     </row>
-    <row r="370" spans="3:92">
+    <row r="370" spans="3:92" x14ac:dyDescent="0.2">
       <c r="J370" s="5"/>
       <c r="AM370" s="6"/>
       <c r="AQ370" s="3"/>
@@ -58764,12 +58764,12 @@
       <c r="AS370" s="3"/>
       <c r="AX370" s="5"/>
     </row>
-    <row r="371" spans="3:92">
+    <row r="371" spans="3:92" x14ac:dyDescent="0.2">
       <c r="J371" s="5"/>
       <c r="AM371" s="6"/>
       <c r="AX371" s="5"/>
     </row>
-    <row r="372" spans="3:92">
+    <row r="372" spans="3:92" x14ac:dyDescent="0.2">
       <c r="J372" s="5"/>
       <c r="AM372" s="6"/>
       <c r="AQ372" s="3"/>
@@ -58779,12 +58779,12 @@
       <c r="CH372" s="3"/>
       <c r="CK372" s="3"/>
     </row>
-    <row r="373" spans="3:92">
+    <row r="373" spans="3:92" x14ac:dyDescent="0.2">
       <c r="J373" s="5"/>
       <c r="AM373" s="6"/>
       <c r="AX373" s="5"/>
     </row>
-    <row r="374" spans="3:92">
+    <row r="374" spans="3:92" x14ac:dyDescent="0.2">
       <c r="C374" s="1"/>
       <c r="D374" s="1"/>
       <c r="E374" s="1"/>
@@ -58798,7 +58798,7 @@
       <c r="AS374" s="3"/>
       <c r="CH374" s="3"/>
     </row>
-    <row r="375" spans="3:92">
+    <row r="375" spans="3:92" x14ac:dyDescent="0.2">
       <c r="C375" s="1"/>
       <c r="D375" s="1"/>
       <c r="E375" s="1"/>
@@ -58812,7 +58812,7 @@
       <c r="AS375" s="3"/>
       <c r="CH375" s="3"/>
     </row>
-    <row r="376" spans="3:92">
+    <row r="376" spans="3:92" x14ac:dyDescent="0.2">
       <c r="C376" s="1"/>
       <c r="D376" s="1"/>
       <c r="E376" s="1"/>
@@ -58826,7 +58826,7 @@
       <c r="AS376" s="3"/>
       <c r="CH376" s="3"/>
     </row>
-    <row r="377" spans="3:92">
+    <row r="377" spans="3:92" x14ac:dyDescent="0.2">
       <c r="C377" s="1"/>
       <c r="D377" s="1"/>
       <c r="E377" s="1"/>
@@ -58842,7 +58842,7 @@
       <c r="CK377" s="3"/>
       <c r="CN377" s="3"/>
     </row>
-    <row r="378" spans="3:92">
+    <row r="378" spans="3:92" x14ac:dyDescent="0.2">
       <c r="C378" s="1"/>
       <c r="D378" s="1"/>
       <c r="E378" s="1"/>
@@ -58858,7 +58858,7 @@
       <c r="CK378" s="3"/>
       <c r="CN378" s="3"/>
     </row>
-    <row r="379" spans="3:92">
+    <row r="379" spans="3:92" x14ac:dyDescent="0.2">
       <c r="C379" s="1"/>
       <c r="D379" s="1"/>
       <c r="E379" s="1"/>
@@ -58873,7 +58873,7 @@
       <c r="CH379" s="3"/>
       <c r="CK379" s="3"/>
     </row>
-    <row r="380" spans="3:92">
+    <row r="380" spans="3:92" x14ac:dyDescent="0.2">
       <c r="C380" s="1"/>
       <c r="D380" s="1"/>
       <c r="E380" s="1"/>
@@ -58888,7 +58888,7 @@
       <c r="CH380" s="3"/>
       <c r="CK380" s="3"/>
     </row>
-    <row r="382" spans="3:92">
+    <row r="382" spans="3:92" x14ac:dyDescent="0.2">
       <c r="C382" s="1"/>
       <c r="D382" s="1"/>
       <c r="E382" s="1"/>
@@ -58900,7 +58900,7 @@
       <c r="AQ382" s="3"/>
       <c r="AR382" s="3"/>
     </row>
-    <row r="383" spans="3:92">
+    <row r="383" spans="3:92" x14ac:dyDescent="0.2">
       <c r="C383" s="1"/>
       <c r="D383" s="1"/>
       <c r="E383" s="1"/>
@@ -58912,7 +58912,7 @@
       <c r="AQ383" s="3"/>
       <c r="AR383" s="3"/>
     </row>
-    <row r="384" spans="3:92">
+    <row r="384" spans="3:92" x14ac:dyDescent="0.2">
       <c r="C384" s="1"/>
       <c r="D384" s="1"/>
       <c r="E384" s="1"/>
@@ -58925,7 +58925,7 @@
       <c r="AR384" s="3"/>
       <c r="BE384" s="3"/>
     </row>
-    <row r="385" spans="3:105">
+    <row r="385" spans="3:105" x14ac:dyDescent="0.2">
       <c r="C385" s="1"/>
       <c r="D385" s="1"/>
       <c r="E385" s="1"/>
@@ -58938,7 +58938,7 @@
       <c r="AR385" s="3"/>
       <c r="BE385" s="3"/>
     </row>
-    <row r="386" spans="3:105">
+    <row r="386" spans="3:105" x14ac:dyDescent="0.2">
       <c r="C386" s="1"/>
       <c r="D386" s="1"/>
       <c r="E386" s="1"/>
@@ -58950,7 +58950,7 @@
       <c r="AQ386" s="3"/>
       <c r="AR386" s="3"/>
     </row>
-    <row r="387" spans="3:105">
+    <row r="387" spans="3:105" x14ac:dyDescent="0.2">
       <c r="C387" s="1"/>
       <c r="D387" s="1"/>
       <c r="E387" s="1"/>
@@ -58964,7 +58964,7 @@
       <c r="CH387" s="3"/>
       <c r="DA387" s="3"/>
     </row>
-    <row r="388" spans="3:105">
+    <row r="388" spans="3:105" x14ac:dyDescent="0.2">
       <c r="AM388" s="2"/>
       <c r="AQ388" s="3"/>
       <c r="AR388" s="3"/>
@@ -58977,12 +58977,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B4E14CE-F38C-41F4-8175-8C11EC1C5043}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>187</v>
       </c>
@@ -58993,7 +58993,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>128</v>
       </c>
@@ -59001,7 +59001,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>134</v>
       </c>
@@ -59012,7 +59012,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>141</v>
       </c>
@@ -59020,7 +59020,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>142</v>
       </c>
@@ -59031,7 +59031,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>143</v>
       </c>
@@ -59042,7 +59042,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>144</v>
       </c>
@@ -59050,7 +59050,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>145</v>
       </c>
@@ -59058,7 +59058,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>146</v>
       </c>
@@ -59066,7 +59066,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>197</v>
       </c>
@@ -59309,15 +59309,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="8508441f-364b-4f89-b1a4-774eaf123e9b" xsi:nil="true"/>
@@ -59335,14 +59326,49 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F780BD8-83B8-46A8-AB88-21C7CF397C84}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F780BD8-83B8-46A8-AB88-21C7CF397C84}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d8cc3f14-1e22-44e3-8129-67bba1aa8a33"/>
+    <ds:schemaRef ds:uri="8508441f-364b-4f89-b1a4-774eaf123e9b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B74A0687-CBD1-4632-A992-64056D2E7329}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9179584A-B226-4942-A24E-2310C95FFCFB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8508441f-364b-4f89-b1a4-774eaf123e9b"/>
+    <ds:schemaRef ds:uri="d8cc3f14-1e22-44e3-8129-67bba1aa8a33"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9179584A-B226-4942-A24E-2310C95FFCFB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B74A0687-CBD1-4632-A992-64056D2E7329}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>